--- a/dev/12.6.2.xlsx
+++ b/dev/12.6.2.xlsx
@@ -5,26 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeremiah Goates\git-repos\Flight_Sim\dev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\git-repos\Flight_Sim\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006D68FF-0721-4A49-93D6-06A73A2D3E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE2B398-B7E7-483A-A5E9-7E205C689084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{7D6525EB-FEF2-421C-8AC9-E2F75E029505}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7D6525EB-FEF2-421C-8AC9-E2F75E029505}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$3:$A$503</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$H$3:$H$503</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$I$3:$I$503</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$J$3:$J$503</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet1!$A$3:$A$503</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet1!$H$3:$H$503</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet1!$I$3:$I$503</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet1!$J$3:$J$503</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
